--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.98527442393715</v>
+        <v>8.772607093889787</v>
       </c>
       <c r="D2" t="n">
-        <v>71.97305166516855</v>
+        <v>11.69562089558989</v>
       </c>
       <c r="E2" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F2" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.01595473879053</v>
+        <v>7.640092645053462</v>
       </c>
       <c r="D3" t="n">
-        <v>67.09468531874495</v>
+        <v>10.90288636429606</v>
       </c>
       <c r="E3" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F3" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.90987990192804</v>
+        <v>7.297855484063306</v>
       </c>
       <c r="D4" t="n">
-        <v>43.96751638674169</v>
+        <v>7.144721412845525</v>
       </c>
       <c r="E4" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F4" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.23982179539077</v>
+        <v>4.751471041751</v>
       </c>
       <c r="D5" t="n">
-        <v>17.54089570752367</v>
+        <v>2.850395552472596</v>
       </c>
       <c r="E5" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F5" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>69.82891349930792</v>
+        <v>11.34719844363754</v>
       </c>
       <c r="D6" t="n">
-        <v>36.08135095059154</v>
+        <v>5.863219529471126</v>
       </c>
       <c r="E6" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F6" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.01429918588273</v>
+        <v>5.527323617705944</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39128778385568</v>
+        <v>5.263584264876548</v>
       </c>
       <c r="E7" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F7" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.17890990095443</v>
+        <v>5.391572858905096</v>
       </c>
       <c r="D8" t="n">
-        <v>32.68820788419561</v>
+        <v>5.311833781181786</v>
       </c>
       <c r="E8" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F8" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>74.19580395092206</v>
+        <v>12.05681814202483</v>
       </c>
       <c r="D9" t="n">
-        <v>31.53740441005057</v>
+        <v>5.124828216633218</v>
       </c>
       <c r="E9" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F9" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.88105753265473</v>
+        <v>8.430671849056393</v>
       </c>
       <c r="D10" t="n">
-        <v>50.81773725747445</v>
+        <v>8.257882304339597</v>
       </c>
       <c r="E10" t="n">
-        <v>14.85856871985126</v>
+        <v>2.414517416975829</v>
       </c>
       <c r="F10" t="n">
-        <v>16.75777694773187</v>
+        <v>2.723138754006429</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
